--- a/Output/Weekly Scan_19 Jul 2026.xlsx
+++ b/Output/Weekly Scan_19 Jul 2026.xlsx
@@ -1794,32 +1794,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>360ONE</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+          <t>No scanner alerts detected for this interval</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A360ONE</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
